--- a/Aula 04/Correção Atividade Aula 03.xlsx
+++ b/Aula 04/Correção Atividade Aula 03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reenye\Documents\SENAI\Excel Básico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reenye\Documents\Excel-Basico\Aula 04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DD76CE1-0625-48AB-B62B-C0A224D09CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67D62DD-9DC2-4E93-9CA0-395EA051BC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C373E67D-7436-4938-B9FA-7917CABDD7E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C373E67D-7436-4938-B9FA-7917CABDD7E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="76">
   <si>
     <t>Produto</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Análise por Artista</t>
+  </si>
+  <si>
+    <t>TAXA DE LUCRO</t>
   </si>
 </sst>
 </file>
@@ -385,7 +388,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -527,23 +530,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -557,67 +549,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -630,66 +647,20 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1025,28 +996,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491FC081-30C8-4151-833C-1CA4FE249502}">
-  <dimension ref="B2:L19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:L19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="12" width="22.7109375" customWidth="1"/>
+    <col min="2" max="12" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="41">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+    </row>
+    <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1100,13 +1079,28 @@
       <c r="G4" s="4">
         <v>5</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="39">
+        <f>AVERAGE(C4,D4,E4,F4,G4)</f>
+        <v>9</v>
+      </c>
+      <c r="I4" s="3">
+        <f>MAX(C4:G4)</f>
+        <v>12</v>
+      </c>
+      <c r="J4" s="3">
+        <f>MIN(C4:G4)</f>
+        <v>5</v>
+      </c>
+      <c r="K4" s="3">
+        <f>LARGE(C4:G4,2)</f>
+        <v>10</v>
+      </c>
+      <c r="L4" s="3">
+        <f>SUM(C4:G4)</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -1125,13 +1119,28 @@
       <c r="G5" s="4">
         <v>10</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="39">
+        <f t="shared" ref="H5:H8" si="0">AVERAGE(C5,D5,E5,F5,G5)</f>
+        <v>7.2</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" ref="I5:I8" si="1">MAX(C5:G5)</f>
+        <v>10</v>
+      </c>
+      <c r="J5" s="3">
+        <f t="shared" ref="J5:J8" si="2">MIN(C5:G5)</f>
+        <v>5</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" ref="K5:K8" si="3">LARGE(C5:G5,2)</f>
+        <v>8</v>
+      </c>
+      <c r="L5" s="3">
+        <f t="shared" ref="L5:L8" si="4">SUM(C5:G5)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1150,13 +1159,28 @@
       <c r="G6" s="4">
         <v>7</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="39">
+        <f t="shared" si="0"/>
+        <v>7.6</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1175,13 +1199,28 @@
       <c r="G7" s="4">
         <v>3</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="39">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1200,118 +1239,169 @@
       <c r="G8" s="4">
         <v>4</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="2:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" s="39">
+        <f t="shared" si="0"/>
+        <v>11.4</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="4"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+    </row>
+    <row r="11" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>31.747</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>59.9</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="5">
+        <f>PRODUCT(L4,D12)</f>
+        <v>2695.5</v>
+      </c>
+      <c r="F12" s="5">
+        <f>E12-PRODUCT(C12,L4)</f>
+        <v>1266.885</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>39.960000000000008</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>99.9</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="5">
+        <f t="shared" ref="E13:E16" si="5">PRODUCT(L5,D13)</f>
+        <v>3596.4</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" ref="F13:F16" si="6">E13-PRODUCT(C13,L5)</f>
+        <v>2157.8399999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>16.513999999999999</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>35.9</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="5">
+        <f t="shared" si="5"/>
+        <v>1364.2</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="6"/>
+        <v>736.66800000000012</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>70.146000000000001</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>129.9</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="5">
+        <f t="shared" si="5"/>
+        <v>2598</v>
+      </c>
+      <c r="F15" s="5">
+        <f t="shared" si="6"/>
+        <v>1195.08</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>8.5860000000000003</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>15.9</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="2:3" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="E16" s="5">
+        <f t="shared" si="5"/>
+        <v>906.30000000000007</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="6"/>
+        <v>416.89800000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="39" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
+      <c r="C18" s="40">
+        <f>SUM(E12:E16)</f>
+        <v>11160.399999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="40">
+        <f>SUM(F12:F16)</f>
+        <v>5773.3710000000001</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1326,49 +1416,49 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7521043-F668-46F1-945A-562113A22F07}">
   <dimension ref="B1:K17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="11" width="20.7109375" customWidth="1"/>
+    <col min="2" max="11" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+    <row r="1" spans="2:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="G2" s="26" t="s">
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="G2" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-    </row>
-    <row r="3" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+    </row>
+    <row r="3" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1387,11 +1477,11 @@
       <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="42">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1410,11 +1500,11 @@
       <c r="H5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="42">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
@@ -1433,11 +1523,11 @@
       <c r="H6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="42">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
@@ -1456,11 +1546,11 @@
       <c r="H7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="42">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
@@ -1479,131 +1569,236 @@
       <c r="H8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="42">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="26" t="s">
+    <row r="9" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="I10" s="27" t="s">
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="I10" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="29"/>
-    </row>
-    <row r="11" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
+      <c r="J10" s="37"/>
+      <c r="K10" s="38"/>
+    </row>
+    <row r="11" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
+    <row r="12" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
-      <c r="I12" s="13" t="s">
+      <c r="C12" s="10">
+        <f>AVERAGE(C4:E4)</f>
+        <v>11</v>
+      </c>
+      <c r="D12" s="10">
+        <f>MAX(C4:E4)</f>
+        <v>12</v>
+      </c>
+      <c r="E12" s="10">
+        <f>SMALL(C4:E4,1)</f>
+        <v>10</v>
+      </c>
+      <c r="F12" s="10">
+        <f>LARGE(C4:E4,2)</f>
+        <v>11</v>
+      </c>
+      <c r="G12" s="11">
+        <f>SUM(C4:E4)</f>
+        <v>33</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
+      <c r="J12" s="43">
+        <f>PRODUCT(G12,I4)</f>
+        <v>825</v>
+      </c>
+      <c r="K12" s="44">
+        <f>C12*I4</f>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-      <c r="I13" s="16" t="s">
+      <c r="C13" s="10">
+        <f t="shared" ref="C13:C16" si="0">AVERAGE(C5:E5)</f>
+        <v>55</v>
+      </c>
+      <c r="D13" s="10">
+        <f t="shared" ref="D13:D16" si="1">MAX(C5:E5)</f>
+        <v>60</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" ref="E13:E16" si="2">SMALL(C5:E5,1)</f>
+        <v>50</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" ref="F13:F16" si="3">LARGE(C5:E5,2)</f>
+        <v>55</v>
+      </c>
+      <c r="G13" s="11">
+        <f t="shared" ref="G13:G16" si="4">SUM(C5:E5)</f>
+        <v>165</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+      <c r="J13" s="43">
+        <f t="shared" ref="J13:J16" si="5">PRODUCT(G13,I5)</f>
+        <v>1320</v>
+      </c>
+      <c r="K13" s="44">
+        <f t="shared" ref="K13:K16" si="6">C13*I5</f>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="15"/>
-      <c r="I14" s="13" t="s">
+      <c r="C14" s="10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="15"/>
-    </row>
-    <row r="15" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="16" t="s">
+      <c r="J14" s="43">
+        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="K14" s="44">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="16" t="s">
+      <c r="C15" s="10">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="18"/>
-    </row>
-    <row r="16" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
+      <c r="J15" s="43">
+        <f t="shared" si="5"/>
+        <v>420</v>
+      </c>
+      <c r="K15" s="44">
+        <f t="shared" si="6"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
-      <c r="I16" s="19" t="s">
+      <c r="C16" s="10">
+        <f t="shared" si="0"/>
+        <v>27.666666666666668</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="G16" s="11">
+        <f t="shared" si="4"/>
+        <v>83</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="20"/>
-      <c r="K16" s="21"/>
-    </row>
-    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J16" s="43">
+        <f t="shared" si="5"/>
+        <v>415</v>
+      </c>
+      <c r="K16" s="44">
+        <f t="shared" si="6"/>
+        <v>138.33333333333334</v>
+      </c>
+    </row>
+    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:E2"/>
@@ -1618,61 +1813,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D60654-B4BF-46FE-8D11-C6504621BEE8}">
   <dimension ref="B2:L17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="12" width="25.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+    <col min="2" max="12" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="30" t="s">
+    <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="G2" s="33" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="G2" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="35"/>
-    </row>
-    <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="31"/>
+    </row>
+    <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>60</v>
       </c>
@@ -1685,16 +1880,31 @@
       <c r="E4" s="4">
         <v>28</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="51"/>
-    </row>
-    <row r="5" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="26">
+        <f>AVERAGE(C4:E4)</f>
+        <v>27.666666666666668</v>
+      </c>
+      <c r="I4" s="26">
+        <f>MAX(C4:E4)</f>
+        <v>30</v>
+      </c>
+      <c r="J4" s="26">
+        <f>MIN(C4:E4)</f>
+        <v>25</v>
+      </c>
+      <c r="K4" s="26">
+        <f>LARGE(C4:E4,2)</f>
+        <v>28</v>
+      </c>
+      <c r="L4" s="27">
+        <f>SUM(C4:E4)</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
@@ -1707,16 +1917,31 @@
       <c r="E5" s="4">
         <v>22</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="49"/>
-    </row>
-    <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="26">
+        <f t="shared" ref="H5:H8" si="0">AVERAGE(C5:E5)</f>
+        <v>20</v>
+      </c>
+      <c r="I5" s="26">
+        <f t="shared" ref="I5:I8" si="1">MAX(C5:E5)</f>
+        <v>22</v>
+      </c>
+      <c r="J5" s="26">
+        <f t="shared" ref="J5:J8" si="2">MIN(C5:E5)</f>
+        <v>18</v>
+      </c>
+      <c r="K5" s="26">
+        <f t="shared" ref="K5:K8" si="3">LARGE(C5:E5,2)</f>
+        <v>20</v>
+      </c>
+      <c r="L5" s="27">
+        <f t="shared" ref="L5:L8" si="4">SUM(C5:E5)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>64</v>
       </c>
@@ -1729,16 +1954,31 @@
       <c r="E6" s="4">
         <v>14</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="51"/>
-    </row>
-    <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="26">
+        <f t="shared" si="0"/>
+        <v>15.333333333333334</v>
+      </c>
+      <c r="I6" s="26">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="J6" s="26">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="K6" s="26">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="L6" s="27">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
@@ -1751,16 +1991,31 @@
       <c r="E7" s="4">
         <v>19</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="49"/>
-    </row>
-    <row r="8" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" s="26">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="I7" s="26">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="J7" s="26">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="K7" s="26">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="L7" s="27">
+        <f t="shared" si="4"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>68</v>
       </c>
@@ -1773,62 +2028,77 @@
       <c r="E8" s="4">
         <v>24</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="53"/>
-    </row>
-    <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="30" t="s">
+      <c r="H8" s="26">
+        <f t="shared" si="0"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="I8" s="26">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="J8" s="26">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="K8" s="26">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="L8" s="27">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="F11" s="33" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="F11" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
-      <c r="J11" s="33" t="s">
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
+      <c r="J11" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="34"/>
-      <c r="L11" s="35"/>
-    </row>
-    <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="31" t="s">
+      <c r="K11" s="30"/>
+      <c r="L11" s="31"/>
+    </row>
+    <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="J12" s="36" t="s">
+      <c r="J12" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="32" t="s">
+      <c r="K12" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="37" t="s">
+      <c r="L12" s="21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>60</v>
       </c>
@@ -1838,18 +2108,30 @@
       <c r="D13" s="4">
         <v>4.5</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="F13" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="39"/>
-      <c r="H13" s="40"/>
-      <c r="J13" s="13" t="s">
+      <c r="G13" s="23">
+        <f>PRODUCT(L4,D13)</f>
+        <v>373.5</v>
+      </c>
+      <c r="H13" s="24">
+        <f>PRODUCT(H4,D13)</f>
+        <v>124.5</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K13" s="10">
+        <f>SUM(C4:E4)</f>
+        <v>83</v>
+      </c>
+      <c r="L13" s="11">
+        <f>PRODUCT(K13,D13)</f>
+        <v>373.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>62</v>
       </c>
@@ -1859,18 +2141,30 @@
       <c r="D14" s="4">
         <v>5</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="43"/>
-      <c r="J14" s="38" t="s">
+      <c r="G14" s="23">
+        <f t="shared" ref="G14:G17" si="5">PRODUCT(L5,D14)</f>
+        <v>300</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" ref="H14:H17" si="6">PRODUCT(H5,D14)</f>
+        <v>100</v>
+      </c>
+      <c r="J14" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="K14" s="39"/>
-      <c r="L14" s="40"/>
-    </row>
-    <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="10">
+        <f t="shared" ref="K14:K17" si="7">SUM(C5:E5)</f>
+        <v>60</v>
+      </c>
+      <c r="L14" s="11">
+        <f t="shared" ref="L14:L17" si="8">PRODUCT(K14,D14)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
@@ -1880,18 +2174,30 @@
       <c r="D15" s="4">
         <v>3.5</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="42"/>
-      <c r="H15" s="44"/>
-      <c r="J15" s="13" t="s">
+      <c r="G15" s="23">
+        <f t="shared" si="5"/>
+        <v>161</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="6"/>
+        <v>53.666666666666671</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="15"/>
-    </row>
-    <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K15" s="10">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="L15" s="11">
+        <f t="shared" si="8"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
         <v>66</v>
       </c>
@@ -1901,18 +2207,30 @@
       <c r="D16" s="4">
         <v>4</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="41"/>
-      <c r="H16" s="43"/>
-      <c r="J16" s="38" t="s">
+      <c r="G16" s="23">
+        <f t="shared" si="5"/>
+        <v>228</v>
+      </c>
+      <c r="H16" s="24">
+        <f t="shared" si="6"/>
+        <v>76</v>
+      </c>
+      <c r="J16" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="K16" s="39"/>
-      <c r="L16" s="40"/>
-    </row>
-    <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K16" s="10">
+        <f t="shared" si="7"/>
+        <v>57</v>
+      </c>
+      <c r="L16" s="11">
+        <f t="shared" si="8"/>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
         <v>68</v>
       </c>
@@ -1922,16 +2240,28 @@
       <c r="D17" s="4">
         <v>3.8</v>
       </c>
-      <c r="F17" s="45" t="s">
+      <c r="F17" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
-      <c r="J17" s="19" t="s">
+      <c r="G17" s="23">
+        <f t="shared" si="5"/>
+        <v>269.8</v>
+      </c>
+      <c r="H17" s="24">
+        <f t="shared" si="6"/>
+        <v>89.933333333333337</v>
+      </c>
+      <c r="J17" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="21"/>
+      <c r="K17" s="10">
+        <f t="shared" si="7"/>
+        <v>71</v>
+      </c>
+      <c r="L17" s="11">
+        <f t="shared" si="8"/>
+        <v>269.8</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Aula 04/Correção Atividade Aula 03.xlsx
+++ b/Aula 04/Correção Atividade Aula 03.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reenye\Documents\Excel-Basico\Aula 04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reenye\Documents\SENAI\Excel Básico\Excel-Basico\Aula 04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67D62DD-9DC2-4E93-9CA0-395EA051BC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AB5351-DD6C-4D80-9631-CA15EDB61E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C373E67D-7436-4938-B9FA-7917CABDD7E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{C373E67D-7436-4938-B9FA-7917CABDD7E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -326,7 +326,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,8 +387,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -530,12 +536,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -611,41 +628,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -660,6 +642,96 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -997,35 +1069,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{491FC081-30C8-4151-833C-1CA4FE249502}">
   <dimension ref="B1:L19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="12" width="22.75" customWidth="1"/>
+    <col min="2" max="12" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="41">
+      <c r="C1" s="28">
         <v>0.15</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="32" t="s">
+    <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-    </row>
-    <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+    </row>
+    <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1079,7 +1151,7 @@
       <c r="G4" s="4">
         <v>5</v>
       </c>
-      <c r="H4" s="39">
+      <c r="H4" s="26">
         <f>AVERAGE(C4,D4,E4,F4,G4)</f>
         <v>9</v>
       </c>
@@ -1100,7 +1172,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -1119,7 +1191,7 @@
       <c r="G5" s="4">
         <v>10</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="26">
         <f t="shared" ref="H5:H8" si="0">AVERAGE(C5,D5,E5,F5,G5)</f>
         <v>7.2</v>
       </c>
@@ -1140,7 +1212,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1159,7 +1231,7 @@
       <c r="G6" s="4">
         <v>7</v>
       </c>
-      <c r="H6" s="39">
+      <c r="H6" s="26">
         <f t="shared" si="0"/>
         <v>7.6</v>
       </c>
@@ -1180,7 +1252,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1199,7 +1271,7 @@
       <c r="G7" s="4">
         <v>3</v>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="26">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1220,7 +1292,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1239,7 +1311,7 @@
       <c r="G8" s="4">
         <v>4</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="26">
         <f t="shared" si="0"/>
         <v>11.4</v>
       </c>
@@ -1260,19 +1332,19 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="33" t="s">
+    <row r="10" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-    </row>
-    <row r="11" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+    </row>
+    <row r="11" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1361,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
@@ -1308,7 +1380,7 @@
         <v>1266.885</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
@@ -1327,7 +1399,7 @@
         <v>2157.8399999999997</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1346,7 +1418,7 @@
         <v>736.66800000000012</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
@@ -1365,7 +1437,7 @@
         <v>1195.08</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
@@ -1384,21 +1456,21 @@
         <v>416.89800000000002</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="39" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3" ht="39" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="27">
         <f>SUM(E12:E16)</f>
         <v>11160.399999999998</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="27">
         <f>SUM(F12:F16)</f>
         <v>5773.3710000000001</v>
       </c>
@@ -1416,26 +1488,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7521043-F668-46F1-945A-562113A22F07}">
   <dimension ref="B1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="11" width="20.75" customWidth="1"/>
+    <col min="2" max="11" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="34" t="s">
+    <row r="1" spans="2:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="G2" s="35" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="G2" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-    </row>
-    <row r="3" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+    </row>
+    <row r="3" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>26</v>
       </c>
@@ -1458,7 +1530,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
@@ -1477,11 +1549,11 @@
       <c r="H4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="29">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1500,11 +1572,11 @@
       <c r="H5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="29">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
@@ -1523,11 +1595,11 @@
       <c r="H6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="29">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
@@ -1546,11 +1618,11 @@
       <c r="H7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="29">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
@@ -1569,27 +1641,27 @@
       <c r="H8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="29">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="35" t="s">
+    <row r="9" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="I10" s="36" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="I10" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="37"/>
-      <c r="K10" s="38"/>
-    </row>
-    <row r="11" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J10" s="41"/>
+      <c r="K10" s="42"/>
+    </row>
+    <row r="11" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>26</v>
       </c>
@@ -1618,7 +1690,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>30</v>
       </c>
@@ -1645,52 +1717,52 @@
       <c r="I12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="43">
+      <c r="J12" s="30">
         <f>PRODUCT(G12,I4)</f>
         <v>825</v>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="31">
         <f>C12*I4</f>
         <v>275</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="43">
         <f t="shared" ref="C13:C16" si="0">AVERAGE(C5:E5)</f>
         <v>55</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="43">
         <f t="shared" ref="D13:D16" si="1">MAX(C5:E5)</f>
         <v>60</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="43">
         <f t="shared" ref="E13:E16" si="2">SMALL(C5:E5,1)</f>
         <v>50</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="43">
         <f t="shared" ref="F13:F16" si="3">LARGE(C5:E5,2)</f>
         <v>55</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="44">
         <f t="shared" ref="G13:G16" si="4">SUM(C5:E5)</f>
         <v>165</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="43">
+      <c r="J13" s="49">
         <f t="shared" ref="J13:J16" si="5">PRODUCT(G13,I5)</f>
         <v>1320</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="50">
         <f t="shared" ref="K13:K16" si="6">C13*I5</f>
         <v>440</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>32</v>
       </c>
@@ -1717,88 +1789,88 @@
       <c r="I14" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="43">
+      <c r="J14" s="30">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="31">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="43">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="43">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="43">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="44">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="49">
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="50">
         <f t="shared" si="6"/>
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="45">
         <f t="shared" si="0"/>
         <v>27.666666666666668</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="45">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="45">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="45">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="46">
         <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="43">
+      <c r="J16" s="47">
         <f t="shared" si="5"/>
         <v>415</v>
       </c>
-      <c r="K16" s="44">
+      <c r="K16" s="48">
         <f t="shared" si="6"/>
         <v>138.33333333333334</v>
       </c>
     </row>
-    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:E2"/>
@@ -1812,30 +1884,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D60654-B4BF-46FE-8D11-C6504621BEE8}">
-  <dimension ref="B2:L17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:L17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.25" customWidth="1"/>
-    <col min="2" max="12" width="25.75" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="12" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+    <row r="2" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="G2" s="29" t="s">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="G2" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="31"/>
-    </row>
-    <row r="3" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="35"/>
+    </row>
+    <row r="3" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="18" t="s">
         <v>51</v>
       </c>
@@ -1867,7 +1939,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="55"/>
       <c r="B4" s="3" t="s">
         <v>60</v>
       </c>
@@ -1880,31 +1953,33 @@
       <c r="E4" s="4">
         <v>28</v>
       </c>
+      <c r="F4" s="55"/>
       <c r="G4" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="56">
         <f>AVERAGE(C4:E4)</f>
         <v>27.666666666666668</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="56">
         <f>MAX(C4:E4)</f>
         <v>30</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="56">
         <f>MIN(C4:E4)</f>
         <v>25</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="56">
         <f>LARGE(C4:E4,2)</f>
         <v>28</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="57">
         <f>SUM(C4:E4)</f>
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="55"/>
       <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
@@ -1917,31 +1992,33 @@
       <c r="E5" s="4">
         <v>22</v>
       </c>
+      <c r="F5" s="55"/>
       <c r="G5" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="58">
         <f t="shared" ref="H5:H8" si="0">AVERAGE(C5:E5)</f>
         <v>20</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="58">
         <f t="shared" ref="I5:I8" si="1">MAX(C5:E5)</f>
         <v>22</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="58">
         <f t="shared" ref="J5:J8" si="2">MIN(C5:E5)</f>
         <v>18</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="58">
         <f t="shared" ref="K5:K8" si="3">LARGE(C5:E5,2)</f>
         <v>20</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="59">
         <f t="shared" ref="L5:L8" si="4">SUM(C5:E5)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="55"/>
       <c r="B6" s="3" t="s">
         <v>64</v>
       </c>
@@ -1954,31 +2031,33 @@
       <c r="E6" s="4">
         <v>14</v>
       </c>
+      <c r="F6" s="55"/>
       <c r="G6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="56">
         <f t="shared" si="0"/>
         <v>15.333333333333334</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="56">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="56">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="56">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="57">
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="55"/>
       <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
@@ -1991,31 +2070,33 @@
       <c r="E7" s="4">
         <v>19</v>
       </c>
+      <c r="F7" s="55"/>
       <c r="G7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="58">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="58">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="58">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="58">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="59">
         <f t="shared" si="4"/>
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="55"/>
       <c r="B8" s="3" t="s">
         <v>68</v>
       </c>
@@ -2028,48 +2109,49 @@
       <c r="E8" s="4">
         <v>24</v>
       </c>
+      <c r="F8" s="55"/>
       <c r="G8" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="60">
         <f t="shared" si="0"/>
         <v>23.666666666666668</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="60">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="60">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="60">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="61">
         <f t="shared" si="4"/>
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="28" t="s">
+    <row r="11" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="F11" s="29" t="s">
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="F11" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="31"/>
-      <c r="J11" s="29" t="s">
+      <c r="G11" s="34"/>
+      <c r="H11" s="35"/>
+      <c r="J11" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="31"/>
-    </row>
-    <row r="12" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K11" s="34"/>
+      <c r="L11" s="35"/>
+    </row>
+    <row r="12" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="18" t="s">
         <v>51</v>
       </c>
@@ -2098,7 +2180,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>60</v>
       </c>
@@ -2131,7 +2213,7 @@
         <v>373.5</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>62</v>
       </c>
@@ -2144,27 +2226,27 @@
       <c r="F14" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="53">
         <f t="shared" ref="G14:G17" si="5">PRODUCT(L5,D14)</f>
         <v>300</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="54">
         <f t="shared" ref="H14:H17" si="6">PRODUCT(H5,D14)</f>
         <v>100</v>
       </c>
       <c r="J14" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="23">
         <f t="shared" ref="K14:K17" si="7">SUM(C5:E5)</f>
         <v>60</v>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="24">
         <f t="shared" ref="L14:L17" si="8">PRODUCT(K14,D14)</f>
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
@@ -2197,7 +2279,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>66</v>
       </c>
@@ -2210,27 +2292,27 @@
       <c r="F16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="53">
         <f t="shared" si="5"/>
         <v>228</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="54">
         <f t="shared" si="6"/>
         <v>76</v>
       </c>
       <c r="J16" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="23">
         <f t="shared" si="7"/>
         <v>57</v>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="24">
         <f t="shared" si="8"/>
         <v>228</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:12" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>68</v>
       </c>
@@ -2243,22 +2325,22 @@
       <c r="F17" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="51">
         <f t="shared" si="5"/>
         <v>269.8</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="52">
         <f t="shared" si="6"/>
         <v>89.933333333333337</v>
       </c>
       <c r="J17" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="45">
         <f t="shared" si="7"/>
         <v>71</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="46">
         <f t="shared" si="8"/>
         <v>269.8</v>
       </c>
